--- a/output/pdf_financials_xlsx/GPH.xlsx
+++ b/output/pdf_financials_xlsx/GPH.xlsx
@@ -928,28 +928,28 @@
         <v>-1.686631</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.045406</v>
+        <v>-2.045406</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.427751</v>
+        <v>-2.427751</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.474591</v>
+        <v>-3.474591</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.610705</v>
+        <v>-1.610705</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.133199</v>
+        <v>-1.133199</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.045118</v>
+        <v>-2.045118</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>8.264771</v>
+        <v>-8.264771</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.698534</v>
+        <v>-5.698534</v>
       </c>
     </row>
     <row r="17">
@@ -1100,28 +1100,28 @@
         <v>-1.686631</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.045406</v>
+        <v>-2.045406</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.427751</v>
+        <v>-2.427751</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.474591</v>
+        <v>-3.474591</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.610705</v>
+        <v>-1.610705</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.133199</v>
+        <v>-1.133199</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.045118</v>
+        <v>-2.045118</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>8.264771</v>
+        <v>-8.264771</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.698534</v>
+        <v>-5.698534</v>
       </c>
     </row>
     <row r="21">
@@ -1202,28 +1202,28 @@
         <v>-1.686631</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.045406</v>
+        <v>-2.045406</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.427751</v>
+        <v>-2.427751</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.474591</v>
+        <v>-3.474591</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.610705</v>
+        <v>-1.610705</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.133199</v>
+        <v>-1.133199</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.045118</v>
+        <v>-2.045118</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>8.264771</v>
+        <v>-8.264771</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5.698534</v>
+        <v>-5.698534</v>
       </c>
     </row>
     <row r="24">
@@ -1304,7 +1304,7 @@
         <v>84.33154999999999</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>102.2703</v>
+        <v>-102.2703</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1312,22 +1312,22 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>173.72955</v>
+        <v>-173.72955</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>23.010071</v>
+        <v>-23.010071</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>28.329975</v>
+        <v>-28.329975</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>40.90236</v>
+        <v>-40.90236</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>68.873092</v>
+        <v>-68.873092</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>94.975567</v>
+        <v>-94.975567</v>
       </c>
     </row>
     <row r="27">
@@ -1340,28 +1340,28 @@
         <v>-1.686631</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.045406</v>
+        <v>-2.045406</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.427751</v>
+        <v>-2.427751</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.474591</v>
+        <v>-3.474591</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.610705</v>
+        <v>-1.610705</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.133199</v>
+        <v>-1.133199</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.045118</v>
+        <v>-2.045118</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>8.264771</v>
+        <v>-8.264771</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.698534</v>
+        <v>-5.698534</v>
       </c>
     </row>
     <row r="28">
@@ -1408,28 +1408,28 @@
         <v>-1.686631</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.045406</v>
+        <v>-2.045406</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.427751</v>
+        <v>-2.427751</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.474591</v>
+        <v>-3.474591</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.610705</v>
+        <v>-1.610705</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.133199</v>
+        <v>-1.133199</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.048959</v>
+        <v>-2.041277</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.266987</v>
+        <v>-8.262555000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5.704908</v>
+        <v>-5.69216</v>
       </c>
     </row>
     <row r="30">
@@ -1494,28 +1494,28 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3627,10 +3627,10 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>12.225926</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>12.029896</v>
       </c>
     </row>
     <row r="93">
@@ -3832,10 +3832,10 @@
         <v>-1.610705</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>1.133199</v>
+        <v>-1.133199</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>2.045118</v>
+        <v>-2.045118</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-8.264771</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.022353</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.249375</v>
       </c>
     </row>
     <row r="104">
@@ -4076,10 +4076,10 @@
         <v>0</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.703928</v>
+        <v>-0.726281</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.975822</v>
+        <v>0.726447</v>
       </c>
     </row>
     <row r="107">
@@ -5351,7 +5351,11 @@
           <t>Prepaids and deposits 9</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -6160,7 +6164,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -9210,7 +9218,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -16050,10 +16062,10 @@
         </is>
       </c>
       <c r="L182" s="5" t="n">
-        <v>8.264771</v>
+        <v>-8.264771</v>
       </c>
       <c r="M182" s="5" t="n">
-        <v>5.698534</v>
+        <v>-5.698534</v>
       </c>
     </row>
     <row r="183">
@@ -16172,10 +16184,10 @@
         </is>
       </c>
       <c r="L184" s="5" t="n">
-        <v>8.346012999999999</v>
+        <v>-8.346012999999999</v>
       </c>
       <c r="M184" s="5" t="n">
-        <v>5.648786</v>
+        <v>-5.648786</v>
       </c>
     </row>
     <row r="185">
@@ -17918,13 +17930,13 @@
         </is>
       </c>
       <c r="I213" s="5" t="n">
-        <v>1.610705</v>
+        <v>-1.610705</v>
       </c>
       <c r="J213" s="5" t="n">
-        <v>1.133199</v>
+        <v>-1.133199</v>
       </c>
       <c r="K213" s="5" t="n">
-        <v>2.045118</v>
+        <v>-2.045118</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -19101,10 +19113,10 @@
         </is>
       </c>
       <c r="H233" s="5" t="n">
-        <v>3.474591</v>
+        <v>-3.474591</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>1.610705</v>
+        <v>-1.610705</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -19462,10 +19474,10 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>2.427751</v>
+        <v>-2.427751</v>
       </c>
       <c r="H239" s="5" t="n">
-        <v>3.474591</v>
+        <v>-3.474591</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -19525,10 +19537,10 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>2.427751</v>
+        <v>-2.427751</v>
       </c>
       <c r="H240" s="5" t="n">
-        <v>3.474591</v>
+        <v>-3.474591</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -20122,10 +20134,10 @@
         </is>
       </c>
       <c r="F250" s="5" t="n">
-        <v>2.045406</v>
+        <v>-2.045406</v>
       </c>
       <c r="G250" s="5" t="n">
-        <v>2.427751</v>
+        <v>-2.427751</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GPH.xlsx
+++ b/output/pdf_financials_xlsx/GPH.xlsx
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001446</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.005184</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.009010000000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005643</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.138247</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.047325</v>
       </c>
     </row>
     <row r="13">
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.686631</v>
+        <v>-1.688077</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.045406</v>
+        <v>-2.05059</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.427751</v>
+        <v>-2.436761</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.474591</v>
+        <v>-3.480234</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.610705</v>
@@ -1358,10 +1358,10 @@
         <v>-2.045118</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-8.264771</v>
+        <v>-8.126524</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.698534</v>
+        <v>-5.651209</v>
       </c>
     </row>
     <row r="28">
@@ -1405,16 +1405,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.686631</v>
+        <v>-1.688077</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.045406</v>
+        <v>-2.05059</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.427751</v>
+        <v>-2.436761</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.474591</v>
+        <v>-3.480234</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.610705</v>
@@ -1426,10 +1426,10 @@
         <v>-2.041277</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-8.262555000000001</v>
+        <v>-8.124307999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.69216</v>
+        <v>-5.644835</v>
       </c>
     </row>
     <row r="30">
@@ -1584,25 +1584,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.512856</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.954924</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.998937</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.723434</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.351081</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.465038</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.218988</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>6.376049</v>
@@ -1652,25 +1652,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.512856</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.954924</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.998937</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.723434</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.351081</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.465038</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.218988</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>6.376049</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.547153</v>
+        <v>0.034297</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.987239</v>
+        <v>1.032315</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.353286</v>
+        <v>0.354349</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.86627</v>
+        <v>0.142836</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.437496</v>
+        <v>0.08641500000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.692651</v>
+        <v>0.227613</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.544764</v>
+        <v>0.325776</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.132329</v>
@@ -4702,10 +4702,10 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.1534</v>
       </c>
     </row>
     <row r="125">
@@ -4736,10 +4736,10 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.1534</v>
       </c>
     </row>
     <row r="126">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -9594,7 +9594,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -15771,7 +15775,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -15834,7 +15838,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -18486,7 +18490,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -19401,7 +19405,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E238" s="5" t="n">

--- a/output/pdf_financials_xlsx/GPH.xlsx
+++ b/output/pdf_financials_xlsx/GPH.xlsx
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.200294</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.153647</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.488313</v>
+        <v>0.688607</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.593368</v>
+        <v>0.747015</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0.806516</v>
@@ -2847,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.085911</v>
       </c>
       <c r="J70" s="3" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         <v>4.282118</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>6.30872</v>
+        <v>6.394631</v>
       </c>
       <c r="J71" s="3" t="n">
         <v>0</v>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.08712399999999999</v>
+        <v>0.001213</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>0.156536</v>
@@ -3207,7 +3207,7 @@
         <v>0.2564313418014027</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.1852042508390413</v>
+        <v>0.187726328597102</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
@@ -4243,13 +4243,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>0.165027</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.299425</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.677709</v>
       </c>
     </row>
     <row r="112">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.110035</v>
       </c>
     </row>
     <row r="117">
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.165027</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.299425</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.677709</v>
       </c>
     </row>
     <row r="135">
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-3.250138</v>
+        <v>-3.549563</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-3.354647</v>
+        <v>-4.032356</v>
       </c>
     </row>
   </sheetData>
@@ -5977,7 +5977,11 @@
           <t>Lease obligations</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -9779,7 +9783,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -9840,7 +9848,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -10743,7 +10755,11 @@
           <t>Purchase of equipment (</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
